--- a/dd-main/v1.0.0/speech/modified.xlsx
+++ b/dd-main/v1.0.0/speech/modified.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>132324234</t>
+          <t>17720499162</t>
         </is>
       </c>
     </row>
